--- a/platform_PiN_output/Somalia___SOM/PiN_step1_Somalia___SOM_1008_03AM.xlsx
+++ b/platform_PiN_output/Somalia___SOM/PiN_step1_Somalia___SOM_1008_03AM.xlsx
@@ -1747,42 +1747,40 @@
         </is>
       </c>
       <c r="C5" s="33" t="n">
-        <v>32213</v>
+        <v/>
       </c>
       <c r="D5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L5" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M5" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N5" s="34" t="n">
+        <v/>
       </c>
       <c r="O5" s="35" t="n">
         <v/>
@@ -1993,8 +1991,10 @@
       <c r="CC5" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="CD5" s="49" t="n">
-        <v>0.1234594728836184</v>
+      <c r="CD5" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2009,42 +2009,40 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>29699</v>
+        <v/>
       </c>
       <c r="D6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L6" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M6" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N6" s="34" t="n">
+        <v/>
       </c>
       <c r="O6" s="35" t="n">
         <v/>
@@ -2255,8 +2253,10 @@
       <c r="CC6" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="CD6" s="49" t="n">
-        <v>0.002053941210141756</v>
+      <c r="CD6" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -7047,41 +7047,61 @@
         </is>
       </c>
       <c r="C25" s="33" t="n">
-        <v>29034</v>
-      </c>
-      <c r="D25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M25" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N25" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O25" s="35" t="n">
@@ -7106,56 +7126,90 @@
         <v/>
       </c>
       <c r="V25" s="39" t="inlineStr"/>
-      <c r="W25" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X25" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y25" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z25" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA25" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL25" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM25" s="43" t="n">
-        <v/>
+      <c r="W25" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X25" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y25" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z25" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA25" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL25" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM25" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN25" s="44" t="n">
         <v/>
@@ -7283,8 +7337,10 @@
       <c r="CC25" s="48" t="n">
         <v/>
       </c>
-      <c r="CD25" s="49" t="n">
-        <v>0</v>
+      <c r="CD25" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -9395,41 +9451,61 @@
         </is>
       </c>
       <c r="C34" s="33" t="n">
-        <v>37688</v>
-      </c>
-      <c r="D34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M34" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N34" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O34" s="35" t="n">
@@ -9454,56 +9530,90 @@
         <v/>
       </c>
       <c r="V34" s="39" t="inlineStr"/>
-      <c r="W34" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X34" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y34" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z34" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA34" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL34" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM34" s="43" t="n">
-        <v/>
+      <c r="W34" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X34" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y34" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z34" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA34" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL34" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM34" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN34" s="44" t="n">
         <v/>
@@ -9631,8 +9741,10 @@
       <c r="CC34" s="48" t="n">
         <v/>
       </c>
-      <c r="CD34" s="49" t="n">
-        <v>0</v>
+      <c r="CD34" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -10453,41 +10565,61 @@
         </is>
       </c>
       <c r="C38" s="33" t="n">
-        <v>49995</v>
-      </c>
-      <c r="D38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M38" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N38" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O38" s="35" t="n">
@@ -10512,56 +10644,90 @@
         <v/>
       </c>
       <c r="V38" s="39" t="inlineStr"/>
-      <c r="W38" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X38" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y38" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z38" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA38" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL38" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM38" s="43" t="n">
-        <v/>
+      <c r="W38" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X38" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y38" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z38" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA38" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL38" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM38" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN38" s="44" t="n">
         <v/>
@@ -10689,8 +10855,10 @@
       <c r="CC38" s="48" t="n">
         <v/>
       </c>
-      <c r="CD38" s="49" t="n">
-        <v>0</v>
+      <c r="CD38" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -10705,41 +10873,61 @@
         </is>
       </c>
       <c r="C39" s="33" t="n">
-        <v>48425</v>
-      </c>
-      <c r="D39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M39" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N39" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O39" s="35" t="n">
@@ -10764,56 +10952,90 @@
         <v/>
       </c>
       <c r="V39" s="39" t="inlineStr"/>
-      <c r="W39" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X39" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y39" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z39" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA39" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL39" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM39" s="43" t="n">
-        <v/>
+      <c r="W39" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X39" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y39" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z39" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA39" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL39" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM39" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN39" s="44" t="n">
         <v/>
@@ -10941,8 +11163,10 @@
       <c r="CC39" s="48" t="n">
         <v/>
       </c>
-      <c r="CD39" s="49" t="n">
-        <v>0</v>
+      <c r="CD39" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -11239,42 +11463,40 @@
         </is>
       </c>
       <c r="C41" s="33" t="n">
-        <v>45305</v>
+        <v/>
       </c>
       <c r="D41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L41" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M41" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N41" s="34" t="n">
+        <v/>
       </c>
       <c r="O41" s="35" t="n">
         <v/>
@@ -11485,8 +11707,10 @@
       <c r="CC41" s="48" t="n">
         <v>0.05997768882472603</v>
       </c>
-      <c r="CD41" s="49" t="n">
-        <v>0.0171283522789979</v>
+      <c r="CD41" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -12025,42 +12249,40 @@
         </is>
       </c>
       <c r="C44" s="33" t="n">
-        <v>45464</v>
+        <v/>
       </c>
       <c r="D44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L44" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M44" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N44" s="34" t="n">
+        <v/>
       </c>
       <c r="O44" s="35" t="n">
         <v/>
@@ -12271,8 +12493,10 @@
       <c r="CC44" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="CD44" s="49" t="n">
-        <v>0.005168924863628365</v>
+      <c r="CD44" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -12287,42 +12511,40 @@
         </is>
       </c>
       <c r="C45" s="33" t="n">
-        <v>177919</v>
+        <v/>
       </c>
       <c r="D45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L45" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M45" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N45" s="34" t="n">
+        <v/>
       </c>
       <c r="O45" s="35" t="n">
         <v/>
@@ -12553,8 +12775,10 @@
       <c r="CC45" s="48" t="n">
         <v>0.1179156594144507</v>
       </c>
-      <c r="CD45" s="49" t="n">
-        <v>0.06442819485271388</v>
+      <c r="CD45" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -12569,42 +12793,40 @@
         </is>
       </c>
       <c r="C46" s="33" t="n">
-        <v>37503</v>
+        <v/>
       </c>
       <c r="D46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L46" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M46" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N46" s="34" t="n">
+        <v/>
       </c>
       <c r="O46" s="35" t="n">
         <v/>
@@ -12815,8 +13037,10 @@
       <c r="CC46" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="CD46" s="49" t="n">
-        <v>0.00554622296882916</v>
+      <c r="CD46" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -17991,41 +18215,61 @@
         </is>
       </c>
       <c r="C67" s="33" t="n">
-        <v>34117</v>
-      </c>
-      <c r="D67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M67" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N67" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O67" s="35" t="n">
@@ -18050,56 +18294,90 @@
         <v/>
       </c>
       <c r="V67" s="39" t="inlineStr"/>
-      <c r="W67" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X67" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y67" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z67" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA67" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL67" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM67" s="43" t="n">
-        <v/>
+      <c r="W67" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X67" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y67" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z67" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA67" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL67" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM67" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN67" s="44" t="n">
         <v/>
@@ -18227,8 +18505,10 @@
       <c r="CC67" s="48" t="n">
         <v/>
       </c>
-      <c r="CD67" s="49" t="n">
-        <v>0</v>
+      <c r="CD67" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -18243,42 +18523,40 @@
         </is>
       </c>
       <c r="C68" s="33" t="n">
-        <v>66972</v>
+        <v/>
       </c>
       <c r="D68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L68" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M68" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N68" s="34" t="n">
+        <v/>
       </c>
       <c r="O68" s="35" t="n">
         <v/>
@@ -18489,8 +18767,10 @@
       <c r="CC68" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="CD68" s="49" t="n">
-        <v>0</v>
+      <c r="CD68" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -18505,41 +18785,61 @@
         </is>
       </c>
       <c r="C69" s="33" t="n">
-        <v>33498</v>
-      </c>
-      <c r="D69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M69" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N69" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O69" s="35" t="n">
@@ -18564,56 +18864,90 @@
         <v/>
       </c>
       <c r="V69" s="39" t="inlineStr"/>
-      <c r="W69" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X69" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y69" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z69" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA69" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL69" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM69" s="43" t="n">
-        <v/>
+      <c r="W69" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X69" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y69" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z69" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA69" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL69" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM69" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN69" s="44" t="n">
         <v/>
@@ -18741,8 +19075,10 @@
       <c r="CC69" s="48" t="n">
         <v/>
       </c>
-      <c r="CD69" s="49" t="n">
-        <v>0</v>
+      <c r="CD69" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -20591,41 +20927,61 @@
         </is>
       </c>
       <c r="C77" s="33" t="n">
-        <v>73943</v>
-      </c>
-      <c r="D77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M77" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N77" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O77" s="35" t="n">
@@ -20650,56 +21006,90 @@
         <v/>
       </c>
       <c r="V77" s="39" t="inlineStr"/>
-      <c r="W77" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X77" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y77" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z77" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA77" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL77" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM77" s="43" t="n">
-        <v/>
+      <c r="W77" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X77" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y77" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z77" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA77" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL77" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM77" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN77" s="44" t="n">
         <v/>
@@ -20827,8 +21217,10 @@
       <c r="CC77" s="48" t="n">
         <v/>
       </c>
-      <c r="CD77" s="49" t="n">
-        <v>0</v>
+      <c r="CD77" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -21105,41 +21497,61 @@
         </is>
       </c>
       <c r="C79" s="33" t="n">
-        <v>40029</v>
-      </c>
-      <c r="D79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M79" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N79" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O79" s="35" t="n">
@@ -21164,56 +21576,90 @@
         <v/>
       </c>
       <c r="V79" s="39" t="inlineStr"/>
-      <c r="W79" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X79" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y79" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z79" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA79" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL79" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM79" s="43" t="n">
-        <v/>
+      <c r="W79" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X79" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y79" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z79" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA79" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL79" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM79" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN79" s="44" t="n">
         <v/>
@@ -21341,8 +21787,10 @@
       <c r="CC79" s="48" t="n">
         <v/>
       </c>
-      <c r="CD79" s="49" t="n">
-        <v>0</v>
+      <c r="CD79" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -21881,42 +22329,40 @@
         </is>
       </c>
       <c r="C82" s="33" t="n">
-        <v>77455</v>
+        <v/>
       </c>
       <c r="D82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L82" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M82" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N82" s="34" t="n">
+        <v/>
       </c>
       <c r="O82" s="35" t="n">
         <v/>
@@ -22127,8 +22573,10 @@
       <c r="CC82" s="48" t="n">
         <v>0.3353127879594553</v>
       </c>
-      <c r="CD82" s="49" t="n">
-        <v>0.004634949325414757</v>
+      <c r="CD82" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -22929,41 +23377,61 @@
         </is>
       </c>
       <c r="C86" s="33" t="n">
-        <v>66770</v>
-      </c>
-      <c r="D86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M86" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N86" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O86" s="35" t="n">
@@ -22988,56 +23456,90 @@
         <v/>
       </c>
       <c r="V86" s="39" t="inlineStr"/>
-      <c r="W86" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X86" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y86" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z86" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA86" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL86" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM86" s="43" t="n">
-        <v/>
+      <c r="W86" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X86" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y86" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z86" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA86" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL86" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM86" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN86" s="44" t="n">
         <v/>
@@ -23165,8 +23667,10 @@
       <c r="CC86" s="48" t="n">
         <v/>
       </c>
-      <c r="CD86" s="49" t="n">
-        <v>0</v>
+      <c r="CD86" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -23181,41 +23685,61 @@
         </is>
       </c>
       <c r="C87" s="33" t="n">
-        <v>75529</v>
-      </c>
-      <c r="D87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M87" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N87" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O87" s="35" t="n">
@@ -23240,56 +23764,90 @@
         <v/>
       </c>
       <c r="V87" s="39" t="inlineStr"/>
-      <c r="W87" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X87" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y87" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z87" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA87" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL87" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM87" s="43" t="n">
-        <v/>
+      <c r="W87" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X87" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y87" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z87" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA87" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL87" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM87" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN87" s="44" t="n">
         <v/>
@@ -23417,8 +23975,10 @@
       <c r="CC87" s="48" t="n">
         <v/>
       </c>
-      <c r="CD87" s="49" t="n">
-        <v>0</v>
+      <c r="CD87" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -23433,41 +23993,61 @@
         </is>
       </c>
       <c r="C88" s="33" t="n">
-        <v>50014</v>
-      </c>
-      <c r="D88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="33" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="D88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="E88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="F88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="G88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="H88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="I88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="J88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="K88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="L88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="M88" s="33" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="N88" s="34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Missing MSNA data for 2024 AND 2025</t>
         </is>
       </c>
       <c r="O88" s="35" t="n">
@@ -23492,56 +24072,90 @@
         <v/>
       </c>
       <c r="V88" s="39" t="inlineStr"/>
-      <c r="W88" s="40" t="n">
-        <v/>
-      </c>
-      <c r="X88" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Y88" s="40" t="n">
-        <v/>
-      </c>
-      <c r="Z88" s="40" t="n">
-        <v/>
-      </c>
-      <c r="AA88" s="41" t="n">
-        <v/>
-      </c>
-      <c r="AB88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AC88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AD88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AE88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AF88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AG88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AH88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AI88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AJ88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AK88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AL88" s="42" t="n">
-        <v/>
-      </c>
-      <c r="AM88" s="43" t="n">
-        <v/>
+      <c r="W88" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="X88" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Y88" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="Z88" s="40" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AA88" s="41" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AB88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AC88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AD88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AE88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AF88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AG88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AH88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AI88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AJ88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AK88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AL88" s="42" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
+      </c>
+      <c r="AM88" s="43" t="inlineStr">
+        <is>
+          <t>Missing MSNA data for 2024 AND 2025</t>
+        </is>
       </c>
       <c r="AN88" s="44" t="n">
         <v/>
@@ -23669,8 +24283,10 @@
       <c r="CC88" s="48" t="n">
         <v/>
       </c>
-      <c r="CD88" s="49" t="n">
-        <v>0</v>
+      <c r="CD88" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -24251,42 +24867,40 @@
         </is>
       </c>
       <c r="C91" s="33" t="n">
-        <v>37711</v>
+        <v/>
       </c>
       <c r="D91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L91" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M91" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N91" s="34" t="n">
+        <v/>
       </c>
       <c r="O91" s="35" t="n">
         <v/>
@@ -24517,8 +25131,10 @@
       <c r="CC91" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="CD91" s="49" t="n">
-        <v>0</v>
+      <c r="CD91" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -24533,42 +25149,40 @@
         </is>
       </c>
       <c r="C92" s="33" t="n">
-        <v>196269</v>
+        <v/>
       </c>
       <c r="D92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="F92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="G92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="H92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="I92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="K92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L92" s="33" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="M92" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v/>
+      </c>
+      <c r="N92" s="34" t="n">
+        <v/>
       </c>
       <c r="O92" s="35" t="n">
         <v/>
@@ -24797,8 +25411,10 @@
       <c r="CC92" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="CD92" s="49" t="n">
-        <v>0</v>
+      <c r="CD92" s="49" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
       </c>
     </row>
   </sheetData>
